--- a/ecv/extraccion_ecv_2021/ecv_2021_wide.xlsx
+++ b/ecv/extraccion_ecv_2021/ecv_2021_wide.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,62 +402,77 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>dep_economica_total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>IMCV_urbano</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estrato_urbano</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_urbano</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_urbano</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_urbano</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_urbano</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_urbano</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>IMCV_rural</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>estrato_rural</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_rural</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_rural</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_rural</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_rural</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_rural</t>
         </is>
       </c>
     </row>
@@ -491,33 +506,36 @@
         <v>8.26524217024841</v>
       </c>
       <c r="J2">
+        <v>84.1058723482852</v>
+      </c>
+      <c r="K2">
         <v>27.7234941176471</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.0532782608695652</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.294586956521739</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>1.47284782608696</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>6.32214395552004</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>24.7627705882353</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>0.0154426470588235</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>1.27287205882353</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>9.768195582056061</v>
       </c>
     </row>
@@ -550,37 +568,37 @@
       <c r="I3">
         <v>10.1343230201866</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>27.4247416666667</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.0103970297029703</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
         <v>1.5031</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>10.9288667602031</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>26.1014</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>0.0194462962962963</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>0</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>1.47088703703704</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>9.423461453010439</v>
       </c>
     </row>
@@ -617,39 +635,45 @@
         <v>11.9655919329255</v>
       </c>
       <c r="J4">
+        <v>47.1166572388089</v>
+      </c>
+      <c r="K4">
         <v>33.9383154761905</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.662072169811321</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.870222641509434</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1.5724429245283</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>1.47360849056604</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>12.4433466086096</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>46.3171504241916</v>
+      </c>
+      <c r="R4">
         <v>27.7705258064516</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>0</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>0.225180555555556</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>1.37886944444444</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>1.48377222222222</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>8.822769103505321</v>
       </c>
     </row>
@@ -686,36 +710,42 @@
         <v>10.8131654651469</v>
       </c>
       <c r="J5">
+        <v>53.4746298372175</v>
+      </c>
+      <c r="K5">
         <v>30.106375625</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.24966682464455</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.419842654028436</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1.44993601895735</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>1.4767663507109</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>10.9476403056874</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>50.8633728847437</v>
+      </c>
+      <c r="R5">
         <v>27.3046285714286</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>0.0954636363636364</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>1.5031</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>9.75404110749697</v>
       </c>
     </row>
@@ -752,34 +782,43 @@
         <v>6.2479229401274</v>
       </c>
       <c r="J6">
+        <v>71.12915392669819</v>
+      </c>
+      <c r="K6">
         <v>28.5407243243243</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.0670276595744681</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>1.29062340425532</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1.45868723404255</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>8.29087615443091</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>60.2822533917393</v>
+      </c>
+      <c r="R6">
         <v>23.9419625</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>0.0285741496598639</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>0.298137414965986</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>1.49836666666667</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>4.93010794196632</v>
+      </c>
+      <c r="X6">
+        <v>77.8248898033824</v>
       </c>
     </row>
     <row r="7">
@@ -815,40 +854,49 @@
         <v>8.668935374094801</v>
       </c>
       <c r="J7">
+        <v>69.0708182191599</v>
+      </c>
+      <c r="K7">
         <v>30.9710805194805</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.253351428571429</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.4459</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1.53972476190476</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1.5031</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>6.72701806245381</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>54.7481317611195</v>
+      </c>
+      <c r="R7">
         <v>26.84906875</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>0.032815625</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>0.1392171875</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>0.36047578125</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>1.5031</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>10.3856789073064</v>
+      </c>
+      <c r="X7">
+        <v>80.1994000316639</v>
       </c>
     </row>
     <row r="8">
@@ -884,37 +932,43 @@
         <v>13.4793580211429</v>
       </c>
       <c r="J8">
+        <v>64.6727088449901</v>
+      </c>
+      <c r="K8">
         <v>30.2086316666667</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.187912631578947</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.361471578947368</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>1.44120105263158</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1.49577578947368</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>19.0601445931395</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>26.6726365853659</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>0.0280026666666667</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>0.295902</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>1.475268</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>9.100441292950631</v>
+      </c>
+      <c r="X8">
+        <v>70.9442978229728</v>
       </c>
     </row>
     <row r="9">
@@ -950,39 +1004,45 @@
         <v>6.74977664703986</v>
       </c>
       <c r="J9">
+        <v>50.7541757175008</v>
+      </c>
+      <c r="K9">
         <v>30.9853470588235</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.508198395721925</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.718354545454545</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>1.4267192513369</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1.5031</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>5.58655179095801</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>48.4264503869269</v>
+      </c>
+      <c r="R9">
         <v>26.3721113636364</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>0.0362103448275862</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>0.216848275862069</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>0.694693103448276</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>1.5031</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>10.2074499430643</v>
       </c>
     </row>
@@ -1019,34 +1079,43 @@
         <v>14.9195393833545</v>
       </c>
       <c r="J10">
+        <v>68.9874379600553</v>
+      </c>
+      <c r="K10">
         <v>28.8731734693878</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.188479487179487</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>1.30016282051282</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>1.46754615384615</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>18.9251171602353</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>52.297376313258</v>
+      </c>
+      <c r="R10">
         <v>26.1833213675214</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>0.0360709090909091</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>0.294281818181818</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>1.49044909090909</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>12.7041252969327</v>
+      </c>
+      <c r="X10">
+        <v>76.8378000573346</v>
       </c>
     </row>
     <row r="11">
@@ -1082,34 +1151,43 @@
         <v>3.19013117571015</v>
       </c>
       <c r="J11">
+        <v>60.7311855486107</v>
+      </c>
+      <c r="K11">
         <v>26.8669465909091</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.0456565217391304</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.200542608695652</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1.37707652173913</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1.49099913043478</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>3.60093886350426</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>52.3194850152341</v>
+      </c>
+      <c r="R11">
         <v>24.8253237288136</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>1.48691860465116</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>2.8032299251421</v>
+      </c>
+      <c r="X11">
+        <v>68.1880538597073</v>
       </c>
     </row>
     <row r="12">
@@ -1145,40 +1223,49 @@
         <v>9.508258630884299</v>
       </c>
       <c r="J12">
+        <v>62.0699578390038</v>
+      </c>
+      <c r="K12">
         <v>28.0297848484849</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.279388990825688</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.405430275229358</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>1.04346146788991</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1.49033302752294</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>7.13435525931989</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>56.171338906706</v>
+      </c>
+      <c r="R12">
         <v>26.5737705882353</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>0.037773381294964</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>0.198838129496403</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>0.630260431654676</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>1.48307697841727</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>11.8415298442</v>
+      </c>
+      <c r="X12">
+        <v>66.6038048317774</v>
       </c>
     </row>
   </sheetData>
